--- a/data/trans_bre/P11_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 19,11</t>
+          <t>2,01; 17,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 23,69</t>
+          <t>8,55; 22,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 24,01</t>
+          <t>9,36; 25,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,19; 28,72</t>
+          <t>12,57; 28,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 93,14</t>
+          <t>7,24; 86,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,52; 135,53</t>
+          <t>34,97; 137,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,19; 138,51</t>
+          <t>37,1; 152,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,35; 116,55</t>
+          <t>36,14; 118,31</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,19; 25,82</t>
+          <t>14,44; 26,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 20,27</t>
+          <t>9,85; 20,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 13,53</t>
+          <t>3,71; 13,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 16,35</t>
+          <t>5,82; 17,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,2; 135,33</t>
+          <t>57,42; 137,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,42; 173,95</t>
+          <t>55,54; 172,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,34; 126,65</t>
+          <t>23,89; 126,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,83; 81,08</t>
+          <t>21,36; 87,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 20,07</t>
+          <t>8,32; 19,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 16,83</t>
+          <t>4,69; 17,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 15,94</t>
+          <t>3,8; 15,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 10,79</t>
+          <t>-2,1; 10,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,01; 190,47</t>
+          <t>49,99; 199,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,88; 130,23</t>
+          <t>23,6; 135,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,24; 155,8</t>
+          <t>21,22; 140,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 37,85</t>
+          <t>-6,29; 37,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 20,52</t>
+          <t>7,36; 19,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 24,24</t>
+          <t>12,07; 24,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 21,78</t>
+          <t>7,9; 21,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 14,22</t>
+          <t>-11,83; 14,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,05; 113,77</t>
+          <t>28,42; 111,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,66; 173,62</t>
+          <t>60,83; 179,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,83; 112,1</t>
+          <t>30,53; 111,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 49,83</t>
+          <t>-32,16; 48,87</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 15,89</t>
+          <t>0,56; 16,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,49; 33,74</t>
+          <t>15,72; 34,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 16,38</t>
+          <t>-0,9; 15,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 16,82</t>
+          <t>2,94; 15,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 140,46</t>
+          <t>2,87; 141,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,38; 197,15</t>
+          <t>59,17; 200,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 94,03</t>
+          <t>-4,74; 84,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,42; 84,06</t>
+          <t>11,59; 80,5</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 17,28</t>
+          <t>2,97; 17,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 12,33</t>
+          <t>-3,53; 11,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 16,71</t>
+          <t>1,14; 16,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,35; 18,31</t>
+          <t>3,67; 19,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 106,61</t>
+          <t>12,36; 104,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 59,73</t>
+          <t>-13,14; 57,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 89,08</t>
+          <t>4,68; 94,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 46,14</t>
+          <t>7,84; 49,08</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 10,71</t>
+          <t>2,56; 10,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 16,56</t>
+          <t>7,05; 16,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,39</t>
+          <t>2,89; 13,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 48,82</t>
+          <t>7,2; 50,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,53; 85,24</t>
+          <t>16,64; 90,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,37; 127,24</t>
+          <t>43,03; 126,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,02; 65,61</t>
+          <t>11,08; 64,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,81; 210,64</t>
+          <t>25,3; 220,85</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 11,27</t>
+          <t>3,22; 11,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,67</t>
+          <t>2,93; 12,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,4</t>
+          <t>6,05; 14,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 25,28</t>
+          <t>10,15; 25,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,09; 69,1</t>
+          <t>15,78; 70,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 57,18</t>
+          <t>10,59; 57,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,57; 102,11</t>
+          <t>33,93; 101,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>53,68; 398,08</t>
+          <t>53,27; 384,29</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,1</t>
+          <t>8,76; 13,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,65</t>
+          <t>10,55; 14,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,34</t>
+          <t>8,2; 12,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,95; 25,86</t>
+          <t>10,11; 29,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>46,65; 76,52</t>
+          <t>45,35; 75,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,66; 81,58</t>
+          <t>53,55; 84,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,65; 70,47</t>
+          <t>41,74; 73,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,78; 118,44</t>
+          <t>36,94; 126,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P11_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P11_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,09</t>
+          <t>20,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>73,72%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 17,88</t>
+          <t>3,91; 19,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 22,98</t>
+          <t>7,82; 23,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 25,43</t>
+          <t>9,24; 24,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 28,64</t>
+          <t>13,6; 27,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 86,6</t>
+          <t>12,97; 90,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,97; 137,58</t>
+          <t>30,95; 136,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,1; 152,76</t>
+          <t>37,62; 150,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,14; 118,31</t>
+          <t>41,76; 115,61</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,49</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,44; 26,23</t>
+          <t>14,07; 25,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 20,35</t>
+          <t>9,57; 19,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 13,65</t>
+          <t>3,88; 13,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 17,09</t>
+          <t>4,64; 15,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,42; 137,59</t>
+          <t>57,0; 139,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,54; 172,94</t>
+          <t>56,21; 172,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,89; 126,25</t>
+          <t>25,3; 125,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,36; 87,21</t>
+          <t>18,37; 77,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 19,82</t>
+          <t>7,96; 20,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 17,34</t>
+          <t>3,6; 16,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 15,4</t>
+          <t>4,01; 16,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 10,93</t>
+          <t>-2,65; 10,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,99; 199,2</t>
+          <t>49,65; 202,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,6; 135,09</t>
+          <t>18,31; 125,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,22; 140,52</t>
+          <t>24,06; 153,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 37,4</t>
+          <t>-6,95; 35,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,51</t>
+          <t>13,86</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 19,98</t>
+          <t>8,15; 20,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 24,41</t>
+          <t>11,76; 24,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 21,37</t>
+          <t>7,81; 21,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 14,06</t>
+          <t>6,43; 21,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,42; 111,01</t>
+          <t>34,3; 120,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,83; 179,18</t>
+          <t>59,37; 181,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,53; 111,18</t>
+          <t>30,6; 112,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 48,87</t>
+          <t>18,5; 86,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,75</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 16,16</t>
+          <t>-0,08; 15,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 34,07</t>
+          <t>16,08; 33,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 15,54</t>
+          <t>-0,53; 16,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 15,81</t>
+          <t>2,59; 15,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 141,99</t>
+          <t>-2,1; 134,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,17; 200,15</t>
+          <t>57,89; 193,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 84,83</t>
+          <t>-3,35; 91,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 80,5</t>
+          <t>9,55; 80,83</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,81</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 17,08</t>
+          <t>3,81; 17,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 11,94</t>
+          <t>-3,46; 11,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 16,89</t>
+          <t>1,49; 16,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 19,38</t>
+          <t>2,6; 18,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,36; 104,22</t>
+          <t>16,83; 109,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 57,93</t>
+          <t>-12,18; 57,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 94,38</t>
+          <t>5,34; 91,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,84; 49,08</t>
+          <t>5,54; 46,43</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,63</t>
+          <t>8,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 10,71</t>
+          <t>2,05; 10,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 16,13</t>
+          <t>7,2; 16,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 13,13</t>
+          <t>3,32; 13,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 50,69</t>
+          <t>3,36; 13,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 90,07</t>
+          <t>12,28; 88,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,03; 126,72</t>
+          <t>41,96; 129,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,08; 64,05</t>
+          <t>12,48; 63,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,3; 220,85</t>
+          <t>10,99; 55,09</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,31</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>121,11%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,22; 11,69</t>
+          <t>3,35; 11,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,93; 12,5</t>
+          <t>3,23; 12,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 14,16</t>
+          <t>5,51; 13,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,15; 25,46</t>
+          <t>6,91; 14,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,78; 70,84</t>
+          <t>16,03; 70,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,59; 57,45</t>
+          <t>12,15; 59,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,93; 101,12</t>
+          <t>29,24; 100,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>53,27; 384,29</t>
+          <t>34,63; 90,36</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,33</t>
+          <t>10,68</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,15</t>
+          <t>9,0; 13,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,55; 14,83</t>
+          <t>10,37; 14,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,56</t>
+          <t>8,04; 12,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,11; 29,18</t>
+          <t>8,53; 12,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,35; 75,93</t>
+          <t>46,29; 75,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53,55; 84,54</t>
+          <t>51,41; 80,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,74; 73,05</t>
+          <t>41,15; 68,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36,94; 126,25</t>
+          <t>30,74; 50,05</t>
         </is>
       </c>
     </row>
